--- a/automation/reports/excel/Execution_Summary.xlsx
+++ b/automation/reports/excel/Execution_Summary.xlsx
@@ -412,7 +412,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B2">
-        <v>510</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -420,7 +420,7 @@
         <v>Passed Tests</v>
       </c>
       <c r="B3">
-        <v>506</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -428,7 +428,7 @@
         <v>Failed Tests</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>Skipped Tests</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>Pass Rate (%)</v>
       </c>
       <c r="B6" t="str">
-        <v>99.22%</v>
+        <v>100.00%</v>
       </c>
     </row>
   </sheetData>
